--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.69025</v>
+        <v>16.71815</v>
       </c>
       <c r="D2" t="n">
-        <v>16.62843</v>
+        <v>16.3099</v>
       </c>
       <c r="E2" t="n">
-        <v>16.73799</v>
+        <v>16.49906</v>
       </c>
       <c r="F2" t="n">
-        <v>42.25614</v>
+        <v>42.93851</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05037</v>
+        <v>0.05124</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81032</v>
+        <v>1.81842</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.88765</v>
+        <v>16.74194</v>
       </c>
       <c r="D3" t="n">
-        <v>16.62296</v>
+        <v>16.56919</v>
       </c>
       <c r="E3" t="n">
-        <v>16.5599</v>
+        <v>16.5989</v>
       </c>
       <c r="F3" t="n">
-        <v>42.26424</v>
+        <v>41.36355</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05137</v>
+        <v>0.0503</v>
       </c>
       <c r="H3" t="n">
-        <v>1.77792</v>
+        <v>1.77853</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.1141</v>
+        <v>17.10907</v>
       </c>
       <c r="D4" t="n">
-        <v>16.70672</v>
+        <v>16.61173</v>
       </c>
       <c r="E4" t="n">
-        <v>16.74638</v>
+        <v>16.87839</v>
       </c>
       <c r="F4" t="n">
-        <v>42.50869</v>
+        <v>42.89217</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05142</v>
+        <v>0.051</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82925</v>
+        <v>1.79051</v>
       </c>
     </row>
   </sheetData>
